--- a/LISTAS_ORDENADAS/MA/Caños Cortina/CAÑO DE HIERRO DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MA/Caños Cortina/CAÑO DE HIERRO DISMAY.xlsx
@@ -784,14 +784,11 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1" s="26">
       <c r="A1" s="25" t="n">
-        <v>45203.68848643584</v>
+        <v>45266</v>
       </c>
       <c r="F1" s="3" t="n"/>
     </row>
     <row r="2" ht="21" customHeight="1" s="26"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="26">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -845,16 +842,6 @@
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="D23" s="11" t="n"/>
     </row>
@@ -922,7 +909,7 @@
         </is>
       </c>
       <c r="D29" s="21" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="26">
@@ -985,7 +972,6 @@
         <v>977</v>
       </c>
     </row>
-    <row r="33"/>
     <row r="34" ht="18" customHeight="1" s="26">
       <c r="A34" s="28" t="n"/>
       <c r="B34" s="28" t="n"/>
@@ -1002,29 +988,24 @@
     </row>
     <row r="36" ht="16.5" customHeight="1" s="26"/>
     <row r="37" ht="16.5" customHeight="1" s="26"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41" ht="19.5" customHeight="1" s="26">
       <c r="A41" s="6" t="n"/>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="4" t="n"/>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.984251968503937" bottom="0.984251968503937" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
